--- a/artfynd/A 49626-2024 artfynd.xlsx
+++ b/artfynd/A 49626-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121180045</v>
+        <v>121180015</v>
       </c>
       <c r="B2" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +799,7 @@
         <v>121179667</v>
       </c>
       <c r="B3" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 49626-2024 artfynd.xlsx
+++ b/artfynd/A 49626-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121180015</v>
+        <v>121179875</v>
       </c>
       <c r="B2" t="n">
         <v>98081</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 49626-2024 artfynd.xlsx
+++ b/artfynd/A 49626-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121179875</v>
+        <v>121180015</v>
       </c>
       <c r="B2" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +799,7 @@
         <v>121179667</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 49626-2024 artfynd.xlsx
+++ b/artfynd/A 49626-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121180015</v>
+        <v>121179667</v>
       </c>
       <c r="B2" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490966</v>
+        <v>491054</v>
       </c>
       <c r="R2" t="n">
-        <v>6955109</v>
+        <v>6955011</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121179667</v>
+        <v>121180045</v>
       </c>
       <c r="B3" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491054</v>
+        <v>490966</v>
       </c>
       <c r="R3" t="n">
-        <v>6955011</v>
+        <v>6955109</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 49626-2024 artfynd.xlsx
+++ b/artfynd/A 49626-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121179667</v>
+        <v>121180045</v>
       </c>
       <c r="B2" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491054</v>
+        <v>490966</v>
       </c>
       <c r="R2" t="n">
-        <v>6955011</v>
+        <v>6955109</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121180045</v>
+        <v>121179667</v>
       </c>
       <c r="B3" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490966</v>
+        <v>491054</v>
       </c>
       <c r="R3" t="n">
-        <v>6955109</v>
+        <v>6955011</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 49626-2024 artfynd.xlsx
+++ b/artfynd/A 49626-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121180045</v>
+        <v>121180015</v>
       </c>
       <c r="B2" t="n">
         <v>98098</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 49626-2024 artfynd.xlsx
+++ b/artfynd/A 49626-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121180015</v>
+        <v>121179875</v>
       </c>
       <c r="B2" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +799,7 @@
         <v>121179667</v>
       </c>
       <c r="B3" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 49626-2024 artfynd.xlsx
+++ b/artfynd/A 49626-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -915,6 +915,800 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121713535</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57357</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>490745</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6954632</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-12-22</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-12-22</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121713823</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57510</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kroktjärnflon, Kroktjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>490698</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6954629</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-12-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-12-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121712608</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78616</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Högberget, Högberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>490953</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6955002</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-12-22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-12-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121713345</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78616</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kroktjärnflon, Kroktjärnflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>490714</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6954686</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-12-22</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-12-22</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121712448</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79698</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kroktjärnbäcken, Kroktjärnbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>490756</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6954976</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-12-22</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-12-22</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121712237</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79697</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kroktjärnbäcken, Kroktjärnbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>490822</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6954826</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-12-22</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-12-22</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121712673</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79697</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Högberget, Högberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>490998</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6954969</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-12-22</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-12-22</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49626-2024 artfynd.xlsx
+++ b/artfynd/A 49626-2024 artfynd.xlsx
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121712608</v>
+        <v>121712448</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>79698</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,34 +933,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Högberget, Högberget, Jmt</t>
+          <t>Kroktjärnbäcken, Kroktjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490953</v>
+        <v>490756</v>
       </c>
       <c r="R4" t="n">
-        <v>6955002</v>
+        <v>6954976</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121713535</v>
+        <v>121713345</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,39 +1045,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+          <t>Kroktjärnflon, Kroktjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490745</v>
+        <v>490714</v>
       </c>
       <c r="R5" t="n">
-        <v>6954632</v>
+        <v>6954686</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121713823</v>
+        <v>121713535</v>
       </c>
       <c r="B6" t="n">
-        <v>57510</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,39 +1157,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kroktjärnflon, Kroktjärnflon, Jmt</t>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490698</v>
+        <v>490745</v>
       </c>
       <c r="R6" t="n">
-        <v>6954629</v>
+        <v>6954632</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121712673</v>
+        <v>121713823</v>
       </c>
       <c r="B7" t="n">
-        <v>79697</v>
+        <v>57510</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1279,34 +1274,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Högberget, Högberget, Jmt</t>
+          <t>Kroktjärnflon, Kroktjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490998</v>
+        <v>490698</v>
       </c>
       <c r="R7" t="n">
-        <v>6954969</v>
+        <v>6954629</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121712448</v>
+        <v>121712608</v>
       </c>
       <c r="B8" t="n">
-        <v>79698</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,34 +1391,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kroktjärnbäcken, Kroktjärnbäcken, Jmt</t>
+          <t>Högberget, Högberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490756</v>
+        <v>490953</v>
       </c>
       <c r="R8" t="n">
-        <v>6954976</v>
+        <v>6955002</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121713345</v>
+        <v>121712673</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,34 +1503,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kroktjärnflon, Kroktjärnflon, Jmt</t>
+          <t>Högberget, Högberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490714</v>
+        <v>490998</v>
       </c>
       <c r="R9" t="n">
-        <v>6954686</v>
+        <v>6954969</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 49626-2024 artfynd.xlsx
+++ b/artfynd/A 49626-2024 artfynd.xlsx
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121712448</v>
+        <v>121712608</v>
       </c>
       <c r="B4" t="n">
-        <v>79698</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,34 +933,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kroktjärnbäcken, Kroktjärnbäcken, Jmt</t>
+          <t>Högberget, Högberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490756</v>
+        <v>490953</v>
       </c>
       <c r="R4" t="n">
-        <v>6954976</v>
+        <v>6955002</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1141,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121713535</v>
+        <v>121712448</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
+        <v>79698</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,39 +1157,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
+          <t>Kroktjärnbäcken, Kroktjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490745</v>
+        <v>490756</v>
       </c>
       <c r="R6" t="n">
-        <v>6954632</v>
+        <v>6954976</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121713823</v>
+        <v>121713535</v>
       </c>
       <c r="B7" t="n">
-        <v>57510</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,39 +1269,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kroktjärnflon, Kroktjärnflon, Jmt</t>
+          <t>Kroktjärnen, Kroktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490698</v>
+        <v>490745</v>
       </c>
       <c r="R7" t="n">
-        <v>6954629</v>
+        <v>6954632</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,7 +1333,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,7 +1343,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121712608</v>
+        <v>121712673</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,21 +1386,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1415,10 +1410,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490953</v>
+        <v>490998</v>
       </c>
       <c r="R8" t="n">
-        <v>6955002</v>
+        <v>6954969</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1455,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121712673</v>
+        <v>121713823</v>
       </c>
       <c r="B9" t="n">
-        <v>79697</v>
+        <v>57510</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,34 +1498,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Högberget, Högberget, Jmt</t>
+          <t>Kroktjärnflon, Kroktjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490998</v>
+        <v>490698</v>
       </c>
       <c r="R9" t="n">
-        <v>6954969</v>
+        <v>6954629</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
